--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1181,7 +1181,7 @@
     <t>2613 - ODARA BRASIL LTDA</t>
   </si>
   <si>
-    <t>6369819200017</t>
+    <t>63698192000171</t>
   </si>
   <si>
     <t>22080045</t>
@@ -1221,6 +1221,9 @@
   </si>
   <si>
     <t>222001 - GERSON NASCIMENTO (PÓS OBRA)</t>
+  </si>
+  <si>
+    <t>13508216000104</t>
   </si>
   <si>
     <t>RUA JORGE COELHO, Nº 147, APTO 141</t>
@@ -3576,13 +3579,13 @@
         <v>402</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>176</v>
+        <v>403</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>9</v>
@@ -3590,16 +3593,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="121">
       <c r="A121" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>221</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>9</v>
@@ -3607,7 +3610,7 @@
     </row>
     <row ht="12.75" customHeight="1" r="122">
       <c r="A122" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>249</v>
@@ -3616,7 +3619,7 @@
         <v>250</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>14</v>
@@ -3624,7 +3627,7 @@
     </row>
     <row ht="12.75" customHeight="1" r="123">
       <c r="A123" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>28</v>
@@ -3641,16 +3644,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="124">
       <c r="A124" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>163</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>14</v>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="419">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1133,7 +1133,7 @@
     <t>RUA PEDROSO ALVARENGA, 896</t>
   </si>
   <si>
-    <t>2608 - MARIA CAROLINA C. M. DE GOUVEA</t>
+    <t>2608 - MARIA CAROLINA C. M. DE GOUVÊA</t>
   </si>
   <si>
     <t>29335672882</t>
@@ -1190,6 +1190,15 @@
     <t>RUA FRANCISCO OTAVIANO, 98 - 401</t>
   </si>
   <si>
+    <t>2614 - CAROLINE DA SILVA RODRIGUES</t>
+  </si>
+  <si>
+    <t>11757819754</t>
+  </si>
+  <si>
+    <t>RUA URBANO SANTOS, 71 - AP 501</t>
+  </si>
+  <si>
     <t>9988 - DÉB. ADM. (DEBITO X CREDITO)</t>
   </si>
   <si>
@@ -1220,7 +1229,7 @@
     <t>RUA PINTASSILGO</t>
   </si>
   <si>
-    <t>222001 - GERSON NASCIMENTO (PÓS OBRA)</t>
+    <t>222001 - GABIUS PART. E ADM. DE BENS LTDA.</t>
   </si>
   <si>
     <t>13508216000104</t>
@@ -1236,6 +1245,12 @@
   </si>
   <si>
     <t>RUA PEDROSO ALVARENGA</t>
+  </si>
+  <si>
+    <t>231401 - LILIAN STUHLBERGER (PÓS OBRA)</t>
+  </si>
+  <si>
+    <t>RUA JOÃO LOURENÇO, 577 - 6º ANDAR</t>
   </si>
   <si>
     <t>231601 - MARCO AURÉLIO SIMÃO FREIRE</t>
@@ -1540,7 +1555,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3514,10 +3529,10 @@
         <v>393</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>14</v>
@@ -3525,16 +3540,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="117">
       <c r="A117" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C117" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>14</v>
@@ -3542,16 +3557,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="118">
       <c r="A118" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>14</v>
@@ -3559,19 +3574,19 @@
     </row>
     <row ht="12.75" customHeight="1" r="119">
       <c r="A119" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="120">
@@ -3582,7 +3597,7 @@
         <v>403</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>404</v>
@@ -3599,7 +3614,7 @@
         <v>406</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>407</v>
@@ -3613,49 +3628,83 @@
         <v>408</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="123">
       <c r="A123" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>268</v>
+        <v>412</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="124">
       <c r="A124" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>412</v>
+        <v>249</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="125">
+      <c r="A125" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="126">
+      <c r="A126" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="D126" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/RelatoriosSiecon/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C0988FC21F52309827B341269182C3234C53EC9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="422">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -632,7 +640,7 @@
     <t>AVENIDA VISCONDE DE ALBUQUERQUE, 29/701</t>
   </si>
   <si>
-    <t xml:space="preserve">2304 -  LEONARDO ALMEIDA BYRRO</t>
+    <t>2304 -  LEONARDO ALMEIDA BYRRO</t>
   </si>
   <si>
     <t>26927536825</t>
@@ -767,7 +775,7 @@
     <t>22630011</t>
   </si>
   <si>
-    <t xml:space="preserve">AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
+    <t>AVENIDA LÚCIO COSTA, 4260, BLOCO 3 -  AP</t>
   </si>
   <si>
     <t>2317 - LUIZ ALBERTO HESS BORGES</t>
@@ -809,7 +817,7 @@
     <t>01049911</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA FORMOSA, 367 -  ANDAR 15</t>
+    <t>RUA FORMOSA, 367 -  ANDAR 15</t>
   </si>
   <si>
     <t>2404 - LUIZ HENRIQUE FRAGA</t>
@@ -1197,6 +1205,15 @@
   </si>
   <si>
     <t>RUA URBANO SANTOS, 71 - AP 501</t>
+  </si>
+  <si>
+    <t>2615 - ANITA BAGGIO BARRETO</t>
+  </si>
+  <si>
+    <t>23484384883</t>
+  </si>
+  <si>
+    <t>RUA URBANO SANTOS, 71 - AP 401</t>
   </si>
   <si>
     <t>9988 - DÉB. ADM. (DEBITO X CREDITO)</t>
@@ -1274,14 +1291,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="28"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1297,38 +1309,42 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1366,19 +1382,79 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1551,22 +1627,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:E126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
-    <col min="2" max="2" width="15" customWidth="1" style="1"/>
-    <col min="3" max="3" width="9" customWidth="1" style="1"/>
-    <col min="4" max="4" width="46.4285714285714" customWidth="1" style="1"/>
-    <col min="5" max="5" width="3.57142857142857" customWidth="1" style="1"/>
-    <col min="6" max="16384" width="11.4285714285714" style="1"/>
+    <col min="1" max="1" width="57.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5546875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row ht="12.75" customHeight="1" r="1">
+    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="2">
+    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1600,7 +1673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="3">
+    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1617,7 +1690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="4">
+    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1634,7 +1707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="5">
+    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1651,7 +1724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="6">
+    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1668,7 +1741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="7">
+    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1685,7 +1758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="8">
+    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1702,7 +1775,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="9">
+    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1719,7 +1792,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="10">
+    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1736,7 +1809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="11">
+    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1753,7 +1826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="12">
+    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1770,7 +1843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="13">
+    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1787,7 +1860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="14">
+    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
@@ -1804,7 +1877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="15">
+    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1821,7 +1894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="16">
+    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
@@ -1838,7 +1911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="17">
+    <row r="17" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -1855,7 +1928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="18">
+    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -1872,7 +1945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="19">
+    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1889,7 +1962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="20">
+    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
@@ -1906,7 +1979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="21">
+    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
@@ -1923,7 +1996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="22">
+    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>81</v>
       </c>
@@ -1940,7 +2013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="23">
+    <row r="23" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>85</v>
       </c>
@@ -1957,7 +2030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="24">
+    <row r="24" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>89</v>
       </c>
@@ -1974,7 +2047,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="25">
+    <row r="25" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>92</v>
       </c>
@@ -1991,7 +2064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="26">
+    <row r="26" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -2008,7 +2081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="27">
+    <row r="27" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>99</v>
       </c>
@@ -2025,7 +2098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="28">
+    <row r="28" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>101</v>
       </c>
@@ -2042,7 +2115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="29">
+    <row r="29" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
@@ -2059,7 +2132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="30">
+    <row r="30" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>108</v>
       </c>
@@ -2076,7 +2149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="31">
+    <row r="31" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>111</v>
       </c>
@@ -2093,7 +2166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="32">
+    <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>115</v>
       </c>
@@ -2110,7 +2183,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="33">
+    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
@@ -2127,7 +2200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="34">
+    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>121</v>
       </c>
@@ -2144,7 +2217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="35">
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>123</v>
       </c>
@@ -2161,7 +2234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="36">
+    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>127</v>
       </c>
@@ -2178,7 +2251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="37">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -2195,7 +2268,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="38">
+    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>132</v>
       </c>
@@ -2212,7 +2285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="39">
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>134</v>
       </c>
@@ -2229,7 +2302,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="40">
+    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>138</v>
       </c>
@@ -2246,7 +2319,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="41">
+    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>142</v>
       </c>
@@ -2263,7 +2336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="42">
+    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>146</v>
       </c>
@@ -2280,7 +2353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="43">
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>148</v>
       </c>
@@ -2297,7 +2370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="44">
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>152</v>
       </c>
@@ -2314,7 +2387,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="45">
+    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>156</v>
       </c>
@@ -2331,7 +2404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="46">
+    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>158</v>
       </c>
@@ -2348,7 +2421,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="47">
+    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>162</v>
       </c>
@@ -2365,7 +2438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="48">
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>165</v>
       </c>
@@ -2382,7 +2455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="49">
+    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>169</v>
       </c>
@@ -2399,7 +2472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="50">
+    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>171</v>
       </c>
@@ -2416,7 +2489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="51">
+    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>175</v>
       </c>
@@ -2433,7 +2506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="52">
+    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>179</v>
       </c>
@@ -2450,7 +2523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="53">
+    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>181</v>
       </c>
@@ -2467,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="54">
+    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>185</v>
       </c>
@@ -2484,7 +2557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="55">
+    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>187</v>
       </c>
@@ -2501,7 +2574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="56">
+    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>191</v>
       </c>
@@ -2518,7 +2591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="57">
+    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>194</v>
       </c>
@@ -2535,7 +2608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="58">
+    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>198</v>
       </c>
@@ -2552,7 +2625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="59">
+    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>202</v>
       </c>
@@ -2569,7 +2642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="60">
+    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>206</v>
       </c>
@@ -2586,7 +2659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="61">
+    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>210</v>
       </c>
@@ -2603,7 +2676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="62">
+    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>213</v>
       </c>
@@ -2620,7 +2693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="63">
+    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>216</v>
       </c>
@@ -2637,7 +2710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="64">
+    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>219</v>
       </c>
@@ -2654,7 +2727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="65">
+    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>223</v>
       </c>
@@ -2671,7 +2744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="66">
+    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>227</v>
       </c>
@@ -2688,7 +2761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="67">
+    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>231</v>
       </c>
@@ -2705,7 +2778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="68">
+    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>234</v>
       </c>
@@ -2722,7 +2795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="69">
+    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>238</v>
       </c>
@@ -2739,7 +2812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="70">
+    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>241</v>
       </c>
@@ -2756,7 +2829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="71">
+    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>245</v>
       </c>
@@ -2773,7 +2846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="72">
+    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>248</v>
       </c>
@@ -2790,7 +2863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="73">
+    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>252</v>
       </c>
@@ -2807,7 +2880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="74">
+    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>256</v>
       </c>
@@ -2824,7 +2897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="75">
+    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>260</v>
       </c>
@@ -2841,7 +2914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="76">
+    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>263</v>
       </c>
@@ -2858,7 +2931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="77">
+    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>266</v>
       </c>
@@ -2875,7 +2948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="78">
+    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>269</v>
       </c>
@@ -2892,7 +2965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="79">
+    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>273</v>
       </c>
@@ -2909,7 +2982,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="80">
+    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>277</v>
       </c>
@@ -2926,7 +2999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="81">
+    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>280</v>
       </c>
@@ -2943,7 +3016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="82">
+    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>283</v>
       </c>
@@ -2960,7 +3033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="83">
+    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>287</v>
       </c>
@@ -2977,7 +3050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="84">
+    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>291</v>
       </c>
@@ -2994,7 +3067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="85">
+    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>293</v>
       </c>
@@ -3011,7 +3084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="86">
+    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>297</v>
       </c>
@@ -3028,7 +3101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="87">
+    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>301</v>
       </c>
@@ -3045,7 +3118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="88">
+    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>304</v>
       </c>
@@ -3062,7 +3135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="89">
+    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>306</v>
       </c>
@@ -3079,7 +3152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="90">
+    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>309</v>
       </c>
@@ -3096,7 +3169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="91">
+    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>312</v>
       </c>
@@ -3113,7 +3186,7 @@
         <v>316</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="92">
+    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>317</v>
       </c>
@@ -3130,7 +3203,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="93">
+    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>320</v>
       </c>
@@ -3147,7 +3220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="94">
+    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>322</v>
       </c>
@@ -3164,7 +3237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="95">
+    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>325</v>
       </c>
@@ -3181,7 +3254,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="96">
+    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>328</v>
       </c>
@@ -3198,7 +3271,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="97">
+    <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>331</v>
       </c>
@@ -3215,7 +3288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="98">
+    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>335</v>
       </c>
@@ -3232,7 +3305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="99">
+    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>338</v>
       </c>
@@ -3249,7 +3322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="100">
+    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>341</v>
       </c>
@@ -3266,7 +3339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="101">
+    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>345</v>
       </c>
@@ -3283,7 +3356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="102">
+    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>348</v>
       </c>
@@ -3300,7 +3373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="103">
+    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>350</v>
       </c>
@@ -3317,7 +3390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="104">
+    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>354</v>
       </c>
@@ -3334,7 +3407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="105">
+    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>358</v>
       </c>
@@ -3351,7 +3424,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="106">
+    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>361</v>
       </c>
@@ -3368,7 +3441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="107">
+    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>364</v>
       </c>
@@ -3385,7 +3458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="108">
+    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>368</v>
       </c>
@@ -3402,7 +3475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="109">
+    <row r="109" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>371</v>
       </c>
@@ -3419,7 +3492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="110">
+    <row r="110" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>373</v>
       </c>
@@ -3436,7 +3509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="111">
+    <row r="111" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>375</v>
       </c>
@@ -3453,7 +3526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="112">
+    <row r="112" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>378</v>
       </c>
@@ -3470,7 +3543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="113">
+    <row r="113" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>381</v>
       </c>
@@ -3487,7 +3560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="114">
+    <row r="114" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>385</v>
       </c>
@@ -3504,7 +3577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="115">
+    <row r="115" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>388</v>
       </c>
@@ -3521,7 +3594,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="116">
+    <row r="116" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>392</v>
       </c>
@@ -3538,7 +3611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="117">
+    <row r="117" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>395</v>
       </c>
@@ -3546,67 +3619,67 @@
         <v>396</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="118">
-      <c r="A118" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C118" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D118" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="119">
-      <c r="A119" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="D119" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="120">
-      <c r="A120" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="121">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>405</v>
       </c>
@@ -3614,7 +3687,7 @@
         <v>406</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>407</v>
@@ -3623,7 +3696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="122">
+    <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>408</v>
       </c>
@@ -3631,7 +3704,7 @@
         <v>409</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>410</v>
@@ -3640,76 +3713,93 @@
         <v>9</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="123">
+    <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>411</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="124">
-      <c r="A124" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B124" s="1" t="s">
+      <c r="D124" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="125">
-      <c r="A125" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="D125" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="126">
-      <c r="A126" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="E126" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="D127" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
-  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
+  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>